--- a/artfynd/A 41079-2026 artfynd.xlsx
+++ b/artfynd/A 41079-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349959</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349961</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137349963</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137349966</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137349965</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137349967</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137349960</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137349969</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>137350001</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137349962</v>
       </c>
       <c r="B11" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137349949</v>
       </c>
       <c r="B12" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137349946</v>
       </c>
       <c r="B13" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137349947</v>
       </c>
       <c r="B14" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137349948</v>
       </c>
       <c r="B15" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>137349945</v>
       </c>
       <c r="B16" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137349956</v>
       </c>
       <c r="B17" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>137349952</v>
       </c>
       <c r="B18" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>137349953</v>
       </c>
       <c r="B19" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>137349950</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>137349955</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137349958</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>137349957</v>
       </c>
       <c r="B23" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>137349951</v>
       </c>
       <c r="B24" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41079-2026 artfynd.xlsx
+++ b/artfynd/A 41079-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349959</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349961</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137349963</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137349966</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137349949</v>
       </c>
       <c r="B12" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137349946</v>
       </c>
       <c r="B13" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137349947</v>
       </c>
       <c r="B14" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137349948</v>
       </c>
       <c r="B15" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>137349945</v>
       </c>
       <c r="B16" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137349956</v>
       </c>
       <c r="B17" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41079-2026 artfynd.xlsx
+++ b/artfynd/A 41079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137349959</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349961</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137349963</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137349966</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137349965</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137349967</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137349960</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137349969</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>137350001</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137349962</v>
+        <v>137349964</v>
       </c>
       <c r="B11" t="n">
-        <v>80581</v>
+        <v>5208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,26 +1734,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1761,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666489</v>
+        <v>666502</v>
       </c>
       <c r="R11" t="n">
-        <v>7022485</v>
+        <v>7022473</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1796,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,21 +1821,6 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1848,51 +1835,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349962</t>
+          <t>https://artportalen.se/Sighting/137349964</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137349949</v>
+        <v>137349962</v>
       </c>
       <c r="B12" t="n">
-        <v>92435</v>
+        <v>80586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Prästberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666490</v>
+        <v>666489</v>
       </c>
       <c r="R12" t="n">
-        <v>7022656</v>
+        <v>7022485</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1924,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,8 +1933,24 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1960,16 +1966,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349949</t>
+          <t>https://artportalen.se/Sighting/137349962</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137349946</v>
+        <v>137349949</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,21 +1983,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +2007,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666512</v>
+        <v>666490</v>
       </c>
       <c r="R13" t="n">
-        <v>7022628</v>
+        <v>7022656</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2036,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2052,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,16 +2078,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349946</t>
+          <t>https://artportalen.se/Sighting/137349949</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137349947</v>
+        <v>137349946</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666518</v>
+        <v>666512</v>
       </c>
       <c r="R14" t="n">
-        <v>7022642</v>
+        <v>7022628</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2148,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,16 +2190,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349947</t>
+          <t>https://artportalen.se/Sighting/137349946</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137349948</v>
+        <v>137349947</v>
       </c>
       <c r="B15" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666489</v>
+        <v>666518</v>
       </c>
       <c r="R15" t="n">
-        <v>7022660</v>
+        <v>7022642</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2260,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,38 +2302,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349948</t>
+          <t>https://artportalen.se/Sighting/137349947</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137349945</v>
+        <v>137349948</v>
       </c>
       <c r="B16" t="n">
-        <v>92127</v>
+        <v>92169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2337,10 +2343,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666512</v>
+        <v>666489</v>
       </c>
       <c r="R16" t="n">
-        <v>7022628</v>
+        <v>7022660</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2372,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,16 +2414,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349945</t>
+          <t>https://artportalen.se/Sighting/137349948</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137349956</v>
+        <v>137349945</v>
       </c>
       <c r="B17" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666444</v>
+        <v>666512</v>
       </c>
       <c r="R17" t="n">
-        <v>7022673</v>
+        <v>7022628</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2484,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,16 +2526,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349956</t>
+          <t>https://artportalen.se/Sighting/137349945</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137349952</v>
+        <v>137349956</v>
       </c>
       <c r="B18" t="n">
-        <v>58031</v>
+        <v>92132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,38 +2543,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Prästberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666519</v>
+        <v>666444</v>
       </c>
       <c r="R18" t="n">
-        <v>7022657</v>
+        <v>7022673</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2600,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,16 +2638,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349952</t>
+          <t>https://artportalen.se/Sighting/137349956</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137349953</v>
+        <v>137349952</v>
       </c>
       <c r="B19" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,29 +2672,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Prästberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666445</v>
+        <v>666519</v>
       </c>
       <c r="R19" t="n">
-        <v>7022663</v>
+        <v>7022657</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2724,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,33 +2754,33 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349953</t>
+          <t>https://artportalen.se/Sighting/137349952</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137349950</v>
+        <v>137349953</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2794,21 +2788,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Prästberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>666488</v>
+        <v>666445</v>
       </c>
       <c r="R20" t="n">
-        <v>7022642</v>
+        <v>7022663</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2840,7 +2842,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,12 +2852,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2881,16 +2878,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349950</t>
+          <t>https://artportalen.se/Sighting/137349953</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137349955</v>
+        <v>137349950</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,10 +2923,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>666434</v>
+        <v>666488</v>
       </c>
       <c r="R21" t="n">
-        <v>7022679</v>
+        <v>7022642</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2961,7 +2958,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2968,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3002,16 +2999,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349955</t>
+          <t>https://artportalen.se/Sighting/137349950</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137349958</v>
+        <v>137349955</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,10 +3044,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666455</v>
+        <v>666434</v>
       </c>
       <c r="R22" t="n">
-        <v>7022710</v>
+        <v>7022679</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3082,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +3089,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3123,16 +3120,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349958</t>
+          <t>https://artportalen.se/Sighting/137349955</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137349957</v>
+        <v>137349958</v>
       </c>
       <c r="B23" t="n">
-        <v>58195</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,21 +3137,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3168,13 +3165,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666478</v>
+        <v>666455</v>
       </c>
       <c r="R23" t="n">
-        <v>7022684</v>
+        <v>7022710</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3203,7 +3200,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3213,7 +3210,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,66 +3241,58 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137349957</t>
+          <t>https://artportalen.se/Sighting/137349958</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137349951</v>
+        <v>137349957</v>
       </c>
       <c r="B24" t="n">
-        <v>58190</v>
+        <v>58196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Prästberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666510</v>
+        <v>666478</v>
       </c>
       <c r="R24" t="n">
-        <v>7022679</v>
+        <v>7022684</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3327,7 +3321,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3337,7 +3331,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3362,6 +3356,130 @@
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137349957</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137349951</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58191</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Prästberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>666510</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7022679</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sidensjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137349951</t>
         </is>
@@ -3392,6 +3510,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41079-2026 artfynd.xlsx
+++ b/artfynd/A 41079-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349959</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349961</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137349963</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137349966</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>137349962</v>
       </c>
       <c r="B12" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137349949</v>
       </c>
       <c r="B13" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>137349946</v>
       </c>
       <c r="B14" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137349947</v>
       </c>
       <c r="B15" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>137349948</v>
       </c>
       <c r="B16" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137349945</v>
       </c>
       <c r="B17" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137349956</v>
       </c>
       <c r="B18" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41079-2026 artfynd.xlsx
+++ b/artfynd/A 41079-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349959</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349961</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137349963</v>
       </c>
       <c r="B4" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137349966</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>137349962</v>
       </c>
       <c r="B12" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137349949</v>
       </c>
       <c r="B13" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>137349946</v>
       </c>
       <c r="B14" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137349947</v>
       </c>
       <c r="B15" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>137349948</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137349945</v>
       </c>
       <c r="B17" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137349956</v>
       </c>
       <c r="B18" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41079-2026 artfynd.xlsx
+++ b/artfynd/A 41079-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349959</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349961</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137349963</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137349966</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>137349962</v>
       </c>
       <c r="B12" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137349949</v>
       </c>
       <c r="B13" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>137349946</v>
       </c>
       <c r="B14" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137349947</v>
       </c>
       <c r="B15" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>137349948</v>
       </c>
       <c r="B16" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137349945</v>
       </c>
       <c r="B17" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137349956</v>
       </c>
       <c r="B18" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41079-2026 artfynd.xlsx
+++ b/artfynd/A 41079-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349959</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349961</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137349963</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137349966</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137349965</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137349967</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137349960</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137349969</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>137350001</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>137349962</v>
       </c>
       <c r="B12" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137349949</v>
       </c>
       <c r="B13" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>137349946</v>
       </c>
       <c r="B14" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137349947</v>
       </c>
       <c r="B15" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>137349948</v>
       </c>
       <c r="B16" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137349945</v>
       </c>
       <c r="B17" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137349956</v>
       </c>
       <c r="B18" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137349952</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>137349953</v>
       </c>
       <c r="B20" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>137349950</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137349955</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137349958</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>137349957</v>
       </c>
       <c r="B24" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>137349951</v>
       </c>
       <c r="B25" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
